--- a/src/main/resources/doc/workorder.xlsx
+++ b/src/main/resources/doc/workorder.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowHeight="17400"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>工单编号</t>
   </si>
@@ -56,7 +56,10 @@
     <t>小区项目名</t>
   </si>
   <si>
-    <t>电梯安装地址</t>
+    <t>电梯名称</t>
+  </si>
+  <si>
+    <t>区域</t>
   </si>
   <si>
     <t>故障原因</t>
@@ -75,6 +78,18 @@
   </si>
   <si>
     <t>疑似死亡人数</t>
+  </si>
+  <si>
+    <t>报警人</t>
+  </si>
+  <si>
+    <t>报警人电话</t>
+  </si>
+  <si>
+    <t>维保人员</t>
+  </si>
+  <si>
+    <t>维保人员电话</t>
   </si>
   <si>
     <t>报警时间</t>
@@ -105,7 +120,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -118,6 +133,13 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -598,156 +620,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,18 +1308,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="19.75" customWidth="1"/>
-    <col min="2" max="9" width="16.7211538461538" customWidth="1"/>
-    <col min="10" max="10" width="35" customWidth="1"/>
-    <col min="11" max="11" width="33.5" customWidth="1"/>
-    <col min="12" max="16" width="16.7211538461538" customWidth="1"/>
-    <col min="17" max="22" width="30.7211538461538" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="4" width="16.7211538461538" customWidth="1"/>
+    <col min="5" max="5" width="30.375" customWidth="1"/>
+    <col min="6" max="6" width="16.7211538461538" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="10" width="16.7211538461538" customWidth="1"/>
+    <col min="11" max="11" width="34.375" customWidth="1"/>
+    <col min="12" max="12" width="32.625" customWidth="1"/>
+    <col min="13" max="21" width="16.7211538461538" customWidth="1"/>
+    <col min="22" max="27" width="30.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,10 +1351,10 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1346,20 +1375,35 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/doc/workorder.xlsx
+++ b/src/main/resources/doc/workorder.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17400"/>
+    <workbookView windowWidth="32460" windowHeight="14400"/>
   </bookViews>
   <sheets>
     <sheet name="历史工单数据" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>工单编号</t>
   </si>
   <si>
     <t>工单类型</t>
-  </si>
-  <si>
-    <t>工单细类</t>
   </si>
   <si>
     <t>场所</t>
@@ -1308,22 +1305,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="4" width="16.7211538461538" customWidth="1"/>
-    <col min="5" max="5" width="30.375" customWidth="1"/>
-    <col min="6" max="6" width="16.7211538461538" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="10" width="16.7211538461538" customWidth="1"/>
-    <col min="11" max="11" width="34.375" customWidth="1"/>
-    <col min="12" max="12" width="32.625" customWidth="1"/>
-    <col min="13" max="21" width="16.7211538461538" customWidth="1"/>
-    <col min="22" max="27" width="30.7211538461538" customWidth="1"/>
+    <col min="2" max="3" width="16.7211538461538" customWidth="1"/>
+    <col min="4" max="4" width="30.375" customWidth="1"/>
+    <col min="5" max="5" width="16.7211538461538" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="9" width="16.7211538461538" customWidth="1"/>
+    <col min="10" max="10" width="34.375" customWidth="1"/>
+    <col min="11" max="11" width="32.625" customWidth="1"/>
+    <col min="12" max="20" width="16.7211538461538" customWidth="1"/>
+    <col min="21" max="26" width="30.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1348,13 +1345,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1372,7 +1369,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
@@ -1384,7 +1381,7 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
@@ -1401,9 +1398,6 @@
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/doc/workorder.xlsx
+++ b/src/main/resources/doc/workorder.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="32460" windowHeight="14400"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="历史工单数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>工单编号</t>
   </si>
@@ -101,10 +101,19 @@
     <t>解救时间</t>
   </si>
   <si>
+    <t>维修完成时间</t>
+  </si>
+  <si>
     <t>回访时间</t>
   </si>
   <si>
     <t>办结工单时间</t>
+  </si>
+  <si>
+    <t>到达时长</t>
+  </si>
+  <si>
+    <t>处理时长</t>
   </si>
 </sst>
 </file>
@@ -117,7 +126,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -137,6 +146,13 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -617,152 +633,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +786,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1305,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
@@ -1317,10 +1336,10 @@
     <col min="10" max="10" width="34.375" customWidth="1"/>
     <col min="11" max="11" width="32.625" customWidth="1"/>
     <col min="12" max="20" width="16.7211538461538" customWidth="1"/>
-    <col min="21" max="26" width="30.7211538461538" customWidth="1"/>
+    <col min="21" max="29" width="30.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,11 +1412,20 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
